--- a/public/data/Auth_MB.xlsx
+++ b/public/data/Auth_MB.xlsx
@@ -5,26 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nurtileu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="👤 Пайдаланушылар" sheetId="1" r:id="rId1"/>
     <sheet name="🎓 Мұғалім профилі" sheetId="2" r:id="rId2"/>
-    <sheet name="📊 Оқушы нәтижелері" sheetId="3" r:id="rId3"/>
-    <sheet name="📚 Сабақ тізімі" sheetId="4" r:id="rId4"/>
-    <sheet name="💬 Пікірлер" sheetId="5" r:id="rId5"/>
-    <sheet name="📈 Статистика" sheetId="6" r:id="rId6"/>
+    <sheet name="📚 Сабақ тізімі" sheetId="4" r:id="rId3"/>
+    <sheet name="💬 Пікірлер" sheetId="5" r:id="rId4"/>
+    <sheet name="📈 Статистика" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="147">
   <si>
     <t>👤 ПАЙДАЛАНУШЫЛАР ДЕРЕКҚОРЫ</t>
   </si>
@@ -266,58 +265,16 @@
     <t>48</t>
   </si>
   <si>
-    <t>📊 ОҚУШЫ НӘТИЖЕЛЕРІ</t>
-  </si>
-  <si>
-    <t>Тест және тапсырмалар бойынша барлық нәтижелер автоматты жиналады</t>
-  </si>
-  <si>
     <t>Оқушы ID</t>
   </si>
   <si>
     <t>Оқушы аты</t>
   </si>
   <si>
-    <t>Тест / Тапсырма атауы</t>
-  </si>
-  <si>
-    <t>Дұрыс</t>
-  </si>
-  <si>
-    <t>Барлығы</t>
-  </si>
-  <si>
-    <t>Пайыз %</t>
-  </si>
-  <si>
     <t>Деңгей</t>
   </si>
   <si>
-    <t>Орындалған күн</t>
-  </si>
-  <si>
-    <t>Абай өмірі — MCQ тест</t>
-  </si>
-  <si>
-    <t>Жақсы</t>
-  </si>
-  <si>
     <t>Дұрыс/Бұрыс тапсырмасы</t>
-  </si>
-  <si>
-    <t>Қанағат.</t>
-  </si>
-  <si>
-    <t>Өте жақсы</t>
-  </si>
-  <si>
-    <t>Қайталаңыз</t>
-  </si>
-  <si>
-    <t>Қайта тапсыру керек</t>
-  </si>
-  <si>
-    <t>Бос орын толтыру</t>
   </si>
   <si>
     <t>📚 САБАҚ ТІЗІМІ (Мұғалім басқарады)</t>
@@ -516,7 +473,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,12 +524,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FF8B3A1E"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF3A5C3A"/>
       <name val="Arial"/>
@@ -591,7 +542,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -640,17 +591,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8B3A1E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -690,9 +631,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -712,30 +653,25 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -746,21 +682,13 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1079,34 +1007,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
     </row>
     <row r="5" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1152,11 +1080,11 @@
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>16</v>
@@ -1188,11 +1116,11 @@
       <c r="C7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="13" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>16</v>
@@ -1228,7 +1156,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>31</v>
@@ -1262,7 +1190,7 @@
         <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>31</v>
@@ -1296,7 +1224,7 @@
         <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>31</v>
@@ -1330,7 +1258,7 @@
         <v>43</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>31</v>
@@ -1360,11 +1288,11 @@
       <c r="C12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="20" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>31</v>
@@ -1398,7 +1326,7 @@
         <v>52</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>16</v>
@@ -1467,7 +1395,7 @@
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" sqref="F6:F500">
       <formula1>"мұғалім,оқушы"</formula1>
     </dataValidation>
@@ -1476,10 +1404,11 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1"/>
-    <hyperlink ref="D7" r:id="rId2"/>
+    <hyperlink ref="D12" r:id="rId1"/>
+    <hyperlink ref="D6" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1496,20 +1425,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="5" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
@@ -1671,370 +1600,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-    </row>
-    <row r="5" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6" s="5">
-        <v>80</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="4">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4">
-        <v>7</v>
-      </c>
-      <c r="H7" s="5">
-        <v>86</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2">
-        <v>5</v>
-      </c>
-      <c r="H8" s="8">
-        <v>60</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="4">
-        <v>5</v>
-      </c>
-      <c r="G9" s="4">
-        <v>7</v>
-      </c>
-      <c r="H9" s="5">
-        <v>71</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="4"/>
-    </row>
-    <row r="10" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3">
-        <v>100</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>5</v>
-      </c>
-      <c r="H11" s="9">
-        <v>40</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="2">
-        <v>4</v>
-      </c>
-      <c r="G12" s="2">
-        <v>5</v>
-      </c>
-      <c r="H12" s="5">
-        <v>80</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="4">
-        <v>3</v>
-      </c>
-      <c r="G13" s="4">
-        <v>3</v>
-      </c>
-      <c r="H13" s="3">
-        <v>100</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="4"/>
-    </row>
-    <row r="14" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:I12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2050,53 +1615,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="B2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="B3" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
     </row>
     <row r="5" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="C5" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="H5" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2106,25 +1671,25 @@
         <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2133,25 +1698,25 @@
         <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2160,22 +1725,22 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>48</v>
@@ -2187,25 +1752,25 @@
         <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>123</v>
+        <v>108</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2214,22 +1779,22 @@
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>48</v>
@@ -2271,7 +1836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:J12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2289,59 +1854,59 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="B2" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="B3" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="5" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2356,19 +1921,19 @@
         <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>20</v>
@@ -2386,19 +1951,19 @@
         <v>32</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F7" s="4">
         <v>4</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>36</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>36</v>
@@ -2416,18 +1981,18 @@
         <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="8"/>
+      <c r="I8" s="7"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2442,19 +2007,19 @@
         <v>40</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F9" s="4">
         <v>3</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>26</v>
@@ -2472,18 +2037,18 @@
         <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="F10" s="2">
         <v>5</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="8"/>
+      <c r="I10" s="7"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2495,7 +2060,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="8"/>
+      <c r="I11" s="7"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2507,7 +2072,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="8"/>
+      <c r="I12" s="7"/>
       <c r="J12" s="2"/>
     </row>
   </sheetData>
@@ -2519,7 +2084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2530,118 +2095,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="B2" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
     </row>
     <row r="4" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="B5" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="10">
         <f>COUNTA('👤 Пайдаланушылар'!C6:C500)</f>
         <v>8</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>149</v>
+      <c r="D5" s="11" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="12">
+      <c r="B6" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="10">
         <f>COUNTIF('👤 Пайдаланушылар'!F6:F500,"мұғалім")</f>
         <v>3</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>149</v>
+      <c r="D6" s="11" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="12">
+      <c r="B7" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="10">
         <f>COUNTIF('👤 Пайдаланушылар'!F6:F500,"оқушы")</f>
         <v>7</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>149</v>
+      <c r="D7" s="11" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="12">
-        <f>COUNTA('📊 Оқушы нәтижелері'!E6:E500)</f>
-        <v>8</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>153</v>
+      <c r="B8" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="10">
+        <f>COUNTA(#REF!)</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="14">
-        <f>IFERROR(AVERAGE('📊 Оқушы нәтижелері'!H6:H500),0)</f>
-        <v>77.125</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>153</v>
+      <c r="B9" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="12">
+        <f>IFERROR(AVERAGE(#REF!),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="12">
+      <c r="B10" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="10">
         <f>COUNTIF('📚 Сабақ тізімі'!G6:G500,"жарияланды")</f>
         <v>4</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>156</v>
+      <c r="D10" s="11" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="12">
+      <c r="B11" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="10">
         <f>COUNTA('💬 Пікірлер'!G6:G500)</f>
         <v>5</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>158</v>
+      <c r="D11" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C12" s="12">
+      <c r="B12" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="10">
         <f>COUNTA('💬 Пікірлер'!I6:I500)</f>
         <v>3</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>158</v>
+      <c r="D12" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
